--- a/salaryEmail/示例数据/2026年10月工资表.xlsx
+++ b/salaryEmail/示例数据/2026年10月工资表.xlsx
@@ -12,7 +12,7 @@
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="2026年10月-正式" sheetId="1" r:id="rId1"/>
+    <sheet name="2026年10月" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/salaryEmail/示例数据/2026年10月工资表.xlsx
+++ b/salaryEmail/示例数据/2026年10月工资表.xlsx
@@ -52,12 +52,18 @@
     <t>绩效奖金</t>
   </si>
   <si>
+    <t>全勤</t>
+  </si>
+  <si>
     <t>加班费</t>
   </si>
   <si>
     <t>&lt;b&gt;应发合计&lt;/b&gt;</t>
   </si>
   <si>
+    <t>&lt;b&gt;减&lt;/b&gt;</t>
+  </si>
+  <si>
     <t>社保</t>
   </si>
   <si>
@@ -67,9 +73,6 @@
     <t>个税</t>
   </si>
   <si>
-    <t>&lt;b&gt;减&lt;/b&gt;</t>
-  </si>
-  <si>
     <t>请假扣款</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>技术部</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>xxx</t>
@@ -1110,19 +1110,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="6" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,16 +1173,19 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2">
         <v>12000</v>
@@ -1192,37 +1197,37 @@
         <v>2000</v>
       </c>
       <c r="G2" s="2">
+        <v>200</v>
+      </c>
+      <c r="H2" s="2">
         <v>800</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>17800</v>
       </c>
-      <c r="I2" s="2">
+      <c r="K2" s="2">
         <v>1200</v>
       </c>
-      <c r="J2" s="2">
+      <c r="L2" s="2">
         <v>800</v>
       </c>
-      <c r="K2" s="2">
+      <c r="M2" s="2">
         <v>640</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
       </c>
       <c r="N2" s="2">
         <v>0</v>
       </c>
       <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
         <v>15160</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1235,8 +1240,9 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1249,8 +1255,9 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1263,8 +1270,9 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1277,8 +1285,9 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1291,8 +1300,9 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -1305,8 +1315,9 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1319,6 +1330,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/salaryEmail/示例数据/2026年10月工资表.xlsx
+++ b/salaryEmail/示例数据/2026年10月工资表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>工号</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>社保</t>
+  </si>
+  <si>
+    <t>医保</t>
+  </si>
+  <si>
+    <t>失业</t>
   </si>
   <si>
     <t>公积金</t>
@@ -1110,21 +1116,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="10" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
     <col min="6" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="10" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="16" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,16 +1182,22 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2">
         <v>12000</v>
@@ -1209,25 +1221,31 @@
         <v>1200</v>
       </c>
       <c r="L2" s="2">
+        <v>90</v>
+      </c>
+      <c r="M2" s="2">
+        <v>10</v>
+      </c>
+      <c r="N2" s="2">
         <v>800</v>
       </c>
-      <c r="M2" s="2">
+      <c r="O2" s="2">
         <v>640</v>
       </c>
-      <c r="N2" s="2">
+      <c r="P2" s="2">
         <v>0</v>
       </c>
-      <c r="O2" s="2">
+      <c r="Q2" s="2">
         <v>0</v>
       </c>
-      <c r="P2" s="2">
+      <c r="R2" s="2">
         <v>15160</v>
       </c>
-      <c r="Q2" t="s">
-        <v>20</v>
+      <c r="S2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:19">
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -1241,8 +1259,10 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:19">
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1256,8 +1276,10 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:19">
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1271,8 +1293,10 @@
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1286,8 +1310,10 @@
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1301,8 +1327,10 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:19">
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -1316,8 +1344,10 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:19">
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1331,6 +1361,8 @@
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/salaryEmail/示例数据/2026年10月工资表.xlsx
+++ b/salaryEmail/示例数据/2026年10月工资表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>工号</t>
   </si>
@@ -100,7 +100,10 @@
     <t>技术部</t>
   </si>
   <si>
-    <t>xxx</t>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>王麻子</t>
   </si>
 </sst>
 </file>
@@ -1241,26 +1244,60 @@
       <c r="R2" s="2">
         <v>15160</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5000</v>
+      </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>5000</v>
+      </c>
     </row>
     <row r="4" spans="1:19">
       <c r="D4" s="2"/>

--- a/salaryEmail/示例数据/2026年10月工资表.xlsx
+++ b/salaryEmail/示例数据/2026年10月工资表.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>工号</t>
   </si>
@@ -98,12 +98,6 @@
   </si>
   <si>
     <t>技术部</t>
-  </si>
-  <si>
-    <t>E002</t>
-  </si>
-  <si>
-    <t>王麻子</t>
   </si>
 </sst>
 </file>
@@ -1246,58 +1240,21 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>5000</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>5000</v>
-      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:19">
       <c r="D4" s="2"/>
